--- a/data/trans_bre/IQ2601_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 19,13</t>
+          <t>0,3; 20,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 9,03</t>
+          <t>-10,69; 9,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 7,02</t>
+          <t>-13,08; 6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 28,45</t>
+          <t>-8,71; 26,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 43,32</t>
+          <t>0,62; 44,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 21,17</t>
+          <t>-20,82; 20,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 11,42</t>
+          <t>-18,86; 10,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 51,77</t>
+          <t>-11,43; 46,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-13,99</t>
+          <t>-14,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-17,27%</t>
+          <t>-18,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 6,11</t>
+          <t>-8,59; 6,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 13,05</t>
+          <t>-3,27; 12,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 8,92</t>
+          <t>-5,22; 8,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 1,45</t>
+          <t>-30,71; -0,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 10,22</t>
+          <t>-12,8; 10,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 28,64</t>
+          <t>-6,18; 28,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 13,9</t>
+          <t>-7,21; 13,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 1,7</t>
+          <t>-36,54; -1,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 8,65</t>
+          <t>-7,35; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 9,53</t>
+          <t>-9,79; 8,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 2,95</t>
+          <t>-13,75; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 32,18</t>
+          <t>-9,43; 29,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,68</t>
+          <t>-8,92; 11,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 19,53</t>
+          <t>-16,21; 17,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 4,86</t>
+          <t>-20,06; 5,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 63,75</t>
+          <t>-12,91; 57,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-12,97</t>
+          <t>-15,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,13%</t>
+          <t>-19,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,35</t>
+          <t>-5,72; 9,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 15,84</t>
+          <t>-1,2; 15,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 12,46</t>
+          <t>-3,42; 12,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 2,78</t>
+          <t>-33,43; 0,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 14,09</t>
+          <t>-7,92; 14,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 39,15</t>
+          <t>-2,58; 37,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 23,07</t>
+          <t>-5,41; 22,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 4,6</t>
+          <t>-39,73; 0,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>-7,24%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,88</t>
+          <t>-1,39; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 7,87</t>
+          <t>-0,62; 7,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,77</t>
+          <t>-4,12; 4,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,71</t>
+          <t>-14,2; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 10,87</t>
+          <t>-2,11; 10,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 17,02</t>
+          <t>-1,2; 16,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,97</t>
+          <t>-6,23; 6,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,9</t>
+          <t>-18,36; 5,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2601_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-5,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.724405043114082</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.525193730078366</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.381944383372282</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.538007034113305</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1929638292635888</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01098472728988491</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.05227631388102763</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1390880067704438</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 20,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-10,69; 9,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; 6,41</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,71; 26,75</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 44,67</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-20,82; 20,35</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-18,86; 10,71</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-11,43; 46,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3026187897587822</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.69052240883575</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.0837659838063</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.712619824840921</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.006150169737336212</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2081546471091981</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1885796455205905</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1142600739350936</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20.28923436951378</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.118519061515437</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.41400515146074</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>26.75054714309193</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4467223199722254</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2035490357166659</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1071251977068201</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.4611262103439516</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,58</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,67</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-18,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,59; 6,3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 12,84</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,22; 8,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-30,71; -0,14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-12,8; 10,07</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,18; 28,74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-7,21; 13,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,54; -1,22</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.9080328671564608</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.584058428784799</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.477592397127947</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-14.6731643405849</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01408754010633117</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.09233638292080514</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02182862200963156</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1823307019962661</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,41</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-8,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.586931442004683</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.270923806645588</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.219321383785023</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-30.70802568621846</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1279721289573591</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.06176472852009465</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.07213543598778903</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3653765739553888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,35; 8,56</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,79; 8,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,75; 3,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,43; 29,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-8,92; 11,52</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-16,21; 17,26</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-20,06; 5,19</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-12,91; 57,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.299562823898189</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>12.84255108574876</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.864145126144516</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.138691640033274</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1007095910466155</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2874234650670239</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1367614967745263</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.0122384525547041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-19,95%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.2505669350943984</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7624596868642142</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.41115352083742</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.790321068905138</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.003192283891834061</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.01431417052363212</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.08268751601557657</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1366836469176687</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,72; 9,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 15,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 12,42</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-33,43; 0,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 14,96</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 37,41</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-5,41; 22,83</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-39,73; 0,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.347207527966643</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.786832871973381</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.74751496689599</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.431252640625114</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.08915012518987427</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1621060868911746</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.200571219367847</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1291239321214505</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.560648997489457</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.386851274237587</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.23655234697989</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>29.53697933173068</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1151595241030128</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1725578256402451</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.05192445095740505</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5744253068768305</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.999522092217754</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.202951720798301</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.220663805388258</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-15.13882611487363</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02941719252485104</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1564444359203513</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07094367440006527</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.199472274974916</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.718364898976787</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.197561474639368</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.417296347352547</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-33.42548862487568</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07922551522550121</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.02580972792881684</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.05409364245083449</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.397328072660466</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.604909475496481</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>15.49977525661741</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>12.42277977623399</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.2059821926930505</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1496074548135364</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3740881430587646</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2282866273957946</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.001117166577930914</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-7,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 6,66</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,62; 7,84</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 4,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-14,2; 3,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 10,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 16,52</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 6,63</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,36; 5,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.470754553104515</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.444153575392439</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2753724849970163</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.313937791468581</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.0377856337824855</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.07020424893541366</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.004280419020507594</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.07242015368393805</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.390513027135787</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6210496730051308</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.119367065284782</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-14.20344281858877</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02109542185678064</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.01202439027529226</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.06231859484019749</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1836431515454182</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.655448949132801</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.837329651548314</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.054620270511721</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.872364268931698</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1034537967837209</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1652468135290768</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.06629612987983668</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05747434705184282</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
